--- a/Documents/SCI_SE_10.ProjectSprintBacklog.xlsx
+++ b/Documents/SCI_SE_10.ProjectSprintBacklog.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9000" activeTab="2"/>
+    <workbookView windowWidth="22188" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint 1" sheetId="1" r:id="rId1"/>
@@ -2602,7 +2602,45 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-GB" sz="2280" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
+                <a:ea typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
+                <a:sym typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="en-GB"/>
+              <a:t>Sprint 1</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" altLang="en-GB"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="1"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout>
         <c:manualLayout>
@@ -3264,9 +3302,57 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:autoTitleDeleted val="1"/>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-GB" sz="2280" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
+                <a:ea typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
+                <a:sym typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="en-GB" b="1"/>
+              <a:t>Sprint 2</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" altLang="en-GB" b="1"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="1"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.0579449874971584"/>
+          <c:y val="0.0355362946912243"/>
+          <c:w val="0.929552170947943"/>
+          <c:h val="0.818028169014084"/>
+        </c:manualLayout>
+      </c:layout>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -3721,7 +3807,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr lang="en-GB" sz="1900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr lang="en-GB" sz="1900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -3778,7 +3864,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr lang="en-GB" sz="1900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr lang="en-GB" sz="1900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -3814,7 +3900,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr lang="en-GB" sz="1900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr lang="en-GB" sz="1900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -3837,7 +3923,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr lang="en-GB" sz="1900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr lang="en-GB" sz="1900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -3876,7 +3962,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr lang="en-GB" sz="1900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr lang="en-GB" sz="1900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -3921,7 +4007,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr lang="en-GB" sz="1900">
+        <a:defRPr lang="en-GB" sz="1900" b="1">
           <a:latin typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
           <a:ea typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
           <a:cs typeface="Times New Roman" panose="02020603050405020304" charset="0"/>
@@ -5038,10 +5124,10 @@
       <xdr:rowOff>84455</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>250825</xdr:colOff>
-      <xdr:row>270</xdr:row>
-      <xdr:rowOff>170180</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>173355</xdr:colOff>
+      <xdr:row>274</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5050,7 +5136,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="3816985" y="53468270"/>
-        <a:ext cx="9151620" cy="5206365"/>
+        <a:ext cx="9904730" cy="5953125"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
